--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2021_tarapaca.xlsx
@@ -42,18 +42,18 @@
     <t xml:space="preserve">Huara</t>
   </si>
   <si>
+    <t xml:space="preserve">Colchane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pozo Almonte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto Hospicio</t>
+  </si>
+  <si>
     <t xml:space="preserve">Camiña</t>
   </si>
   <si>
-    <t xml:space="preserve">Colchane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pozo Almonte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alto Hospicio</t>
-  </si>
-  <si>
     <t xml:space="preserve">Iquique</t>
   </si>
   <si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:15</t>
+    <t xml:space="preserve">2026-09-10 00:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -530,7 +530,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -543,7 +543,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -556,7 +556,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1401</v>
+        <v>1107</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -569,7 +569,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1107</v>
+        <v>1402</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:19</t>
+    <t xml:space="preserve">2026-09-18 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
